--- a/results/kpi_matrix.xlsx
+++ b/results/kpi_matrix.xlsx
@@ -487,17 +487,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -521,30 +522,35 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Schema Mutation (PR #67)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Code Laziness</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Database Integrity</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Language Consistency</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Event Loop Congestion</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Import Cascade</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Notes / Failure Details</t>
         </is>
@@ -563,30 +569,35 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>No Laziness</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Polish in comment [utils.py]: Zapobiega duplikowaniu handler; Polish in comment [utils.py]: Standardowy format z datą, poz; Polish in comment [utils.py]: Handler zapisujący logi do pli</t>
         </is>
@@ -605,30 +616,35 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>No Laziness</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Polish in comment [database.py]: Import centralnych ustawień; Polish in comment [database.py]: Można również sparametryzować ; Polish in string literal [database.py]: 
     Inicjalizacja bazy danych...</t>
@@ -648,30 +664,35 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>No Laziness</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Polish in docstring [exceptions.py]: Module; Polish in docstring [exceptions.py]: FinanceException; Polish in docstring [exceptions.py]: AssetNotFoundException</t>
         </is>
@@ -690,30 +711,35 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t>No Laziness</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Polish in comment [config.py]: Ścieżka do asynchronicznej baz; Polish in comment [config.py]: Nazwa wyświetlana aplikacji (n; Polish in comment [config.py]: Globalna instancja konfiguracj</t>
         </is>
@@ -730,40 +756,45 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>No Laziness</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Missing alias_generator and populate_by_name (No camelCase configured at all); Polish in comment [config.py]: Instancja ustawień (singleton); Polish in docstring [config.py]: Module; Polish in docstring [config.py]: Settings; services.py not found</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Missing alias_generator and populate_by_name (No camelCase configured at all); Grok Free did not implement database column migration; Polish in comment [config.py]: Instancja ustawień (singleton); Polish in docstring [config.py]: Module; Polish in docstring [config.py]: Settings; services.py not found</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
